--- a/project/excel/portable_microhaplotype_object.xlsx
+++ b/project/excel/portable_microhaplotype_object.xlsx
@@ -1225,7 +1225,7 @@
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>host_subject_id</t>
+          <t>host_subject_name</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
